--- a/Assets/Data/GameData.xlsx
+++ b/Assets/Data/GameData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/startingwave02/Desktop/Projects/3D/P032_FrogTD/Assets/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4A58021-AF66-364B-AE28-1252A4935080}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A06E7420-4CBF-6648-94C9-EA43283C09C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5140" yWindow="1820" windowWidth="28100" windowHeight="17380" activeTab="1" xr2:uid="{3F49F6D9-933F-C746-9861-018452375900}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="18">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -86,7 +86,19 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>이름</t>
+    <t>resource_name</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이름 코드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>리소스명</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>01_Frog</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -95,10 +107,6 @@
   </si>
   <si>
     <t>이동 속도</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>체력</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -494,24 +502,27 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B86D02F-1298-2244-946A-F37B07854EB4}">
-  <dimension ref="B2:G5"/>
+  <dimension ref="B2:H5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
   <sheetData>
-    <row r="2" spans="2:7">
+    <row r="2" spans="2:8">
       <c r="B2" t="s">
         <v>0</v>
       </c>
       <c r="C2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" t="s">
         <v>3</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>6</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="2:7">
+    <row r="3" spans="2:8">
       <c r="B3" t="s">
         <v>1</v>
       </c>
@@ -519,38 +530,47 @@
         <v>4</v>
       </c>
       <c r="D3" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
       </c>
-      <c r="G3" s="1"/>
-    </row>
-    <row r="4" spans="2:7">
+      <c r="F3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H3" s="1"/>
+    </row>
+    <row r="4" spans="2:8">
       <c r="B4" t="s">
         <v>2</v>
       </c>
       <c r="C4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" t="s">
         <v>11</v>
       </c>
-      <c r="E4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="2:7">
+      <c r="F4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="2:8">
       <c r="B5">
         <v>100001</v>
       </c>
-      <c r="C5">
-        <v>200001</v>
+      <c r="C5" t="s">
+        <v>15</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>100001</v>
       </c>
       <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
         <v>1</v>
       </c>
     </row>
@@ -562,30 +582,33 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CA4A611-3FC7-BB49-943F-F3D9268DC105}">
-  <dimension ref="B2:G5"/>
+  <dimension ref="B2:H5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
   <sheetData>
-    <row r="2" spans="2:7">
+    <row r="2" spans="2:8">
       <c r="B2" t="s">
         <v>0</v>
       </c>
       <c r="C2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" t="s">
         <v>3</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>5</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>6</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>7</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="2:7">
+    <row r="3" spans="2:8">
       <c r="B3" t="s">
         <v>1</v>
       </c>
@@ -593,7 +616,7 @@
         <v>4</v>
       </c>
       <c r="D3" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -601,40 +624,46 @@
       <c r="F3" t="s">
         <v>9</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H3" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="2:7">
+    <row r="4" spans="2:8">
       <c r="B4" t="s">
         <v>2</v>
       </c>
       <c r="C4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4" t="s">
         <v>11</v>
       </c>
-      <c r="F4" t="s">
-        <v>13</v>
-      </c>
       <c r="G4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="2:7">
+        <v>16</v>
+      </c>
+      <c r="H4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="2:8">
       <c r="B5">
         <v>200001</v>
       </c>
-      <c r="C5">
+      <c r="C5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5">
         <v>200001</v>
       </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
       <c r="E5">
         <v>1</v>
       </c>
@@ -642,6 +671,9 @@
         <v>1</v>
       </c>
       <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
         <v>1</v>
       </c>
     </row>
